--- a/code/アラジン入力用配台計画/アラジン入力用_配台計画.xlsx
+++ b/code/アラジン入力用配台計画/アラジン入力用_配台計画.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="176">
   <si>
     <t>依頼NO</t>
   </si>
@@ -164,6 +164,50 @@
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
+      <t>（シス計）3600</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）4500</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）7200</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
       <t>（シス計）2100</t>
     </r>
   </si>
@@ -174,6 +218,72 @@
         <sz val="9.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
+      <t>（現アラ計）6300</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）6600</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）4500</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）4500</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）3300</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）4500</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
       <t>（現アラ計）0</t>
     </r>
     <r>
@@ -186,13 +296,96 @@
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
+      <t>（シス計）6600</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
       <t>（シス計）1500</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
+    <t>W8-6</t>
+  </si>
+  <si>
+    <t>190989F</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>2026/08/06</t>
+  </si>
+  <si>
+    <t>8/18</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>4500</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>3600</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）3600</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）3600</t>
+    </r>
+  </si>
+  <si>
+    <t>W8-7</t>
+  </si>
+  <si>
+    <t>190991R</t>
+  </si>
+  <si>
+    <t>2026/08/07</t>
+  </si>
+  <si>
+    <t>8/21</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="9.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
@@ -204,7 +397,6 @@
     </r>
     <r>
       <rPr>
-        <color indexed="9"/>
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
@@ -214,19 +406,17 @@
   <si>
     <r>
       <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）7200</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
@@ -236,29 +426,38 @@
   <si>
     <r>
       <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）6300</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）6600</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）2400</t>
+    </r>
+  </si>
+  <si>
+    <t>W8-10</t>
+  </si>
+  <si>
+    <t>190994Y</t>
+  </si>
+  <si>
+    <t>2026/08/19</t>
+  </si>
+  <si>
+    <t>8/25</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="9.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
@@ -270,7 +469,55 @@
     </r>
     <r>
       <rPr>
-        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）4200</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）300</t>
+    </r>
+  </si>
+  <si>
+    <t>W8-8</t>
+  </si>
+  <si>
+    <t>190996M</t>
+  </si>
+  <si>
+    <t>2026/08/17</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
@@ -278,9 +525,81 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
+    <t>W8-9</t>
+  </si>
+  <si>
+    <t>190997H</t>
+  </si>
+  <si>
+    <t>2026/08/18</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）2700</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1800</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <t>W8-12</t>
+  </si>
+  <si>
+    <t>191292V</t>
+  </si>
+  <si>
+    <t>8/26</t>
+  </si>
+  <si>
+    <t>W8-13</t>
+  </si>
+  <si>
+    <t>191293B</t>
+  </si>
+  <si>
+    <t>2026/08/20</t>
+  </si>
+  <si>
+    <t>8/27</t>
+  </si>
+  <si>
+    <t>3300</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="9.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
@@ -292,6 +611,858 @@
     </r>
     <r>
       <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）1800</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）1500</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）5000</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）10000</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1000</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）10000</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）6045</t>
+    </r>
+  </si>
+  <si>
+    <t>C8-4</t>
+  </si>
+  <si>
+    <t>190303W/190304R</t>
+  </si>
+  <si>
+    <t>SEC</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）5000</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）10000</t>
+    </r>
+  </si>
+  <si>
+    <t>C8-2</t>
+  </si>
+  <si>
+    <t>190302F</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）5000</t>
+    </r>
+  </si>
+  <si>
+    <t>JR260801</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1045</t>
+  </si>
+  <si>
+    <t>NG (差 +45)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1000</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）1045</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）800</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1400</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）1400</t>
+    </r>
+  </si>
+  <si>
+    <t>T8-1</t>
+  </si>
+  <si>
+    <t>190005G、191202Z（195ｍ）</t>
+  </si>
+  <si>
+    <t>エンボス</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）800</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）800</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）800</t>
+    </r>
+  </si>
+  <si>
+    <t>T8-3</t>
+  </si>
+  <si>
+    <t>191203T</t>
+  </si>
+  <si>
+    <t>8/20</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）600</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）600</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）200</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1250</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）760</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）190</t>
+    </r>
+  </si>
+  <si>
+    <t>C8-7</t>
+  </si>
+  <si>
+    <t>191291A</t>
+  </si>
+  <si>
+    <t>スリット</t>
+  </si>
+  <si>
+    <t>2026/08/10</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）200</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）200</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <t>A8-1</t>
+  </si>
+  <si>
+    <t>分割</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）100</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）950</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）760</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）0</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）190</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1200</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）4500</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）4800</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）4500</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）3600</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1500</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）5100</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）900</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）5100</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）5100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1800</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）2400</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）5100</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）5400</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）4200</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1800</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
         <color indexed="9"/>
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
@@ -318,59 +1489,13 @@
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
-      <t>（シス計）6600</t>
-    </r>
-  </si>
-  <si>
-    <t>W8-6</t>
-  </si>
-  <si>
-    <t>190989F</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>2026/08/06</t>
-  </si>
-  <si>
-    <t>8/18</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>4500</t>
-  </si>
-  <si>
-    <t>900</t>
-  </si>
-  <si>
-    <t>3600</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）3600</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）2100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>（シス計）4500</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color indexed="9"/>
         <sz val="9.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
@@ -382,26 +1507,27 @@
     </r>
     <r>
       <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）1500</t>
-    </r>
-  </si>
-  <si>
-    <t>W8-7</t>
-  </si>
-  <si>
-    <t>190991R</t>
-  </si>
-  <si>
-    <t>2026/08/07</t>
-  </si>
-  <si>
-    <t>8/21</t>
-  </si>
-  <si>
-    <t>0</t>
+        <color indexed="9"/>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）4200</t>
+    </r>
+  </si>
+  <si>
+    <t>W8-5</t>
+  </si>
+  <si>
+    <t>190987B</t>
+  </si>
+  <si>
+    <t>検査</t>
+  </si>
+  <si>
+    <t>1800</t>
+  </si>
+  <si>
+    <t>2700</t>
   </si>
   <si>
     <r>
@@ -420,6 +1546,64 @@
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
+      <t>（シス計）2700</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）4500</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）2400</t>
+    </r>
+  </si>
+  <si>
+    <t>W7-22</t>
+  </si>
+  <si>
+    <t>190764G</t>
+  </si>
+  <si>
+    <t>検反</t>
+  </si>
+  <si>
+    <t>2026/08/03</t>
+  </si>
+  <si>
+    <t>2400</t>
+  </si>
+  <si>
+    <t>1200</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1200</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
       <t>（シス計）0</t>
     </r>
   </si>
@@ -440,7 +1624,47 @@
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
-      <t>（シス計）2100</t>
+      <t>（シス計）1200</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）1500</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）3000</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）900</t>
     </r>
   </si>
   <si>
@@ -460,39 +1684,7 @@
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
-      <t>（シス計）2400</t>
-    </r>
-  </si>
-  <si>
-    <t>W8-10</t>
-  </si>
-  <si>
-    <t>190994Y</t>
-  </si>
-  <si>
-    <t>2026/08/19</t>
-  </si>
-  <si>
-    <t>8/25</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）4500</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）4200</t>
+      <t>（シス計）3600</t>
     </r>
   </si>
   <si>
@@ -512,17 +1704,48 @@
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
-      <t>（シス計）300</t>
-    </r>
-  </si>
-  <si>
-    <t>W8-8</t>
-  </si>
-  <si>
-    <t>190996M</t>
-  </si>
-  <si>
-    <t>2026/08/17</t>
+      <t>（シス計）600</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）2100</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（現アラ計）2400</t>
+    </r>
+    <r>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.0"/>
+        <rFont val="BIZ UDPゴシック"/>
+      </rPr>
+      <t>（シス計）0</t>
+    </r>
   </si>
   <si>
     <r>
@@ -541,1243 +1764,7 @@
         <sz val="12.0"/>
         <rFont val="BIZ UDPゴシック"/>
       </rPr>
-      <t>（シス計）4500</t>
-    </r>
-  </si>
-  <si>
-    <t>W8-9</t>
-  </si>
-  <si>
-    <t>190997H</t>
-  </si>
-  <si>
-    <t>2026/08/18</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）2700</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1800</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <t>W8-12</t>
-  </si>
-  <si>
-    <t>191292V</t>
-  </si>
-  <si>
-    <t>8/26</t>
-  </si>
-  <si>
-    <t>W8-13</t>
-  </si>
-  <si>
-    <t>191293B</t>
-  </si>
-  <si>
-    <t>2026/08/20</t>
-  </si>
-  <si>
-    <t>8/27</t>
-  </si>
-  <si>
-    <t>3300</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）3300</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）1800</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）4000</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）5000</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）3600</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）10000</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1000</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）10000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）6045</t>
-    </r>
-  </si>
-  <si>
-    <t>C8-3</t>
-  </si>
-  <si>
-    <t>190300B/190301K</t>
-  </si>
-  <si>
-    <t>SEC</t>
-  </si>
-  <si>
-    <t>8/11</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>6400</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）4000</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）3600</t>
-    </r>
-  </si>
-  <si>
-    <t>C8-4</t>
-  </si>
-  <si>
-    <t>190303W/190304R</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）5000</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）10000</t>
-    </r>
-  </si>
-  <si>
-    <t>C8-2</t>
-  </si>
-  <si>
-    <t>190302F</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）5000</t>
-    </r>
-  </si>
-  <si>
-    <t>JR260801</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>1045</t>
-  </si>
-  <si>
-    <t>NG (差 +45)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1000</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）1045</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1400</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）2200</t>
-    </r>
-  </si>
-  <si>
-    <t>T8-1</t>
-  </si>
-  <si>
-    <t>190005G、191202Z（195ｍ）</t>
-  </si>
-  <si>
-    <t>エンボス</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>1600</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）800</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）1600</t>
-    </r>
-  </si>
-  <si>
-    <t>T8-3</t>
-  </si>
-  <si>
-    <t>191203T</t>
-  </si>
-  <si>
-    <t>8/20</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）600</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）600</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）200</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）500</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1250</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）760</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）190</t>
-    </r>
-  </si>
-  <si>
-    <t>C8-7</t>
-  </si>
-  <si>
-    <t>191291A</t>
-  </si>
-  <si>
-    <t>スリット</t>
-  </si>
-  <si>
-    <t>2026/08/10</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）200</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）200</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <t>W8-11</t>
-  </si>
-  <si>
-    <t>191049F/191295F</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>NG (差 +100)</t>
-  </si>
-  <si>
-    <t>A8-1</t>
-  </si>
-  <si>
-    <t>分割</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）100</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <t>950</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）950</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）760</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）190</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）3300</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）4500</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）4800</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1500</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）2400</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）5100</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
       <t>（シス計）900</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）5100</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）5100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1800</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）2400</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）5100</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）5400</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）4200</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1800</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）4500</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）4500</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color indexed="9"/>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）4200</t>
-    </r>
-  </si>
-  <si>
-    <t>W8-5</t>
-  </si>
-  <si>
-    <t>190987B</t>
-  </si>
-  <si>
-    <t>検査</t>
-  </si>
-  <si>
-    <t>3900</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）4500</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）3900</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）900</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）4500</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）3600</t>
-    </r>
-  </si>
-  <si>
-    <t>W7-22</t>
-  </si>
-  <si>
-    <t>190764G</t>
-  </si>
-  <si>
-    <t>検反</t>
-  </si>
-  <si>
-    <t>2026/08/03</t>
-  </si>
-  <si>
-    <t>2400</t>
-  </si>
-  <si>
-    <t>1200</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1200</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <t>A8-2</t>
-  </si>
-  <si>
-    <t>接続</t>
-  </si>
-  <si>
-    <t>2026-08-17</t>
-  </si>
-  <si>
-    <t>2100</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）2100</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）1500</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）3000</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）900</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）0</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）600</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（現アラ計）2400</t>
-    </r>
-    <r>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12.0"/>
-        <rFont val="BIZ UDPゴシック"/>
-      </rPr>
-      <t>（シス計）0</t>
     </r>
   </si>
   <si>
@@ -2196,49 +2183,49 @@
         <v>32</v>
       </c>
       <c r="N2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="14" t="s">
+      <c r="U2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="V2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="W2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="X2" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="14" t="s">
+      <c r="Y2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA2" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="Y2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AB2" s="14" t="s">
         <v>39</v>
-      </c>
-      <c r="AB2" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="AC2" s="14" t="s">
         <v>31</v>
@@ -2284,11 +2271,11 @@
       <c r="L3" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>50</v>
+      <c r="N3" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="O3" t="s" s="10">
         <v>31</v>
@@ -2341,19 +2328,19 @@
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s" s="6">
         <v>51</v>
-      </c>
-      <c r="B4" t="s" s="6">
-        <v>52</v>
       </c>
       <c r="C4" t="s" s="6">
         <v>42</v>
       </c>
       <c r="D4" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s" s="6">
         <v>53</v>
-      </c>
-      <c r="E4" t="s" s="6">
-        <v>54</v>
       </c>
       <c r="F4" t="s" s="8">
         <v>45</v>
@@ -2362,7 +2349,7 @@
         <v>46</v>
       </c>
       <c r="H4" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I4" t="s" s="7">
         <v>46</v>
@@ -2398,13 +2385,13 @@
         <v>31</v>
       </c>
       <c r="T4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="U4" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="U4" s="11" t="s">
+      <c r="V4" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="W4" t="s" s="10">
         <v>31</v>
@@ -2433,19 +2420,19 @@
     </row>
     <row r="5" ht="33.0" customHeight="true">
       <c r="A5" t="s" s="6">
+        <v>58</v>
+      </c>
+      <c r="B5" t="s" s="6">
         <v>59</v>
-      </c>
-      <c r="B5" t="s" s="6">
-        <v>60</v>
       </c>
       <c r="C5" t="s" s="6">
         <v>42</v>
       </c>
       <c r="D5" t="s" s="6">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s" s="6">
         <v>61</v>
-      </c>
-      <c r="E5" t="s" s="6">
-        <v>62</v>
       </c>
       <c r="F5" t="s" s="8">
         <v>45</v>
@@ -2454,7 +2441,7 @@
         <v>46</v>
       </c>
       <c r="H5" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I5" t="s" s="7">
         <v>46</v>
@@ -2496,22 +2483,22 @@
         <v>31</v>
       </c>
       <c r="V5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="W5" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="X5" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="Y5" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="Z5" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="AA5" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="W5" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="X5" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Y5" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="Z5" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="AA5" s="11" t="s">
-        <v>64</v>
       </c>
       <c r="AB5" t="s" s="10">
         <v>31</v>
@@ -2525,19 +2512,19 @@
     </row>
     <row r="6" ht="33.0" customHeight="true">
       <c r="A6" t="s" s="6">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s" s="6">
         <v>65</v>
-      </c>
-      <c r="B6" t="s" s="6">
-        <v>66</v>
       </c>
       <c r="C6" t="s" s="6">
         <v>42</v>
       </c>
       <c r="D6" t="s" s="6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s" s="6">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s" s="8">
         <v>45</v>
@@ -2546,7 +2533,7 @@
         <v>46</v>
       </c>
       <c r="H6" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I6" t="s" s="7">
         <v>46</v>
@@ -2585,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="V6" t="s" s="10">
         <v>31</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="X6" t="s" s="10">
         <v>31</v>
@@ -2617,19 +2604,19 @@
     </row>
     <row r="7" ht="33.0" customHeight="true">
       <c r="A7" t="s" s="6">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s" s="6">
         <v>69</v>
-      </c>
-      <c r="B7" t="s" s="6">
-        <v>70</v>
       </c>
       <c r="C7" t="s" s="6">
         <v>42</v>
       </c>
       <c r="D7" t="s" s="6">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s" s="6">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s" s="8">
         <v>45</v>
@@ -2638,7 +2625,7 @@
         <v>46</v>
       </c>
       <c r="H7" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s" s="7">
         <v>46</v>
@@ -2677,16 +2664,16 @@
         <v>31</v>
       </c>
       <c r="U7" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="V7" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="V7" s="10" t="s">
-        <v>73</v>
-      </c>
       <c r="W7" t="s" s="10">
         <v>31</v>
       </c>
       <c r="X7" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y7" t="s" s="12">
         <v>31</v>
@@ -2709,19 +2696,19 @@
     </row>
     <row r="8" ht="33.0" customHeight="true">
       <c r="A8" t="s" s="6">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s" s="6">
         <v>74</v>
-      </c>
-      <c r="B8" t="s" s="6">
-        <v>75</v>
       </c>
       <c r="C8" t="s" s="6">
         <v>42</v>
       </c>
       <c r="D8" t="s" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s" s="6">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F8" t="s" s="8">
         <v>45</v>
@@ -2730,7 +2717,7 @@
         <v>46</v>
       </c>
       <c r="H8" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I8" t="s" s="7">
         <v>46</v>
@@ -2775,7 +2762,7 @@
         <v>31</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="X8" t="s" s="10">
         <v>31</v>
@@ -2787,7 +2774,7 @@
         <v>31</v>
       </c>
       <c r="AA8" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AB8" t="s" s="10">
         <v>31</v>
@@ -2801,31 +2788,31 @@
     </row>
     <row r="9" ht="33.0" customHeight="true">
       <c r="A9" t="s" s="6">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s" s="6">
         <v>77</v>
-      </c>
-      <c r="B9" t="s" s="6">
-        <v>78</v>
       </c>
       <c r="C9" t="s" s="6">
         <v>42</v>
       </c>
       <c r="D9" t="s" s="6">
+        <v>78</v>
+      </c>
+      <c r="E9" t="s" s="6">
         <v>79</v>
-      </c>
-      <c r="E9" t="s" s="6">
-        <v>80</v>
       </c>
       <c r="F9" t="s" s="8">
         <v>45</v>
       </c>
       <c r="G9" t="s" s="7">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I9" t="s" s="7">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J9" t="s" s="8">
         <v>45</v>
@@ -2870,19 +2857,19 @@
         <v>31</v>
       </c>
       <c r="X9" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y9" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="Z9" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="AA9" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="Y9" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="Z9" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="AA9" s="11" t="s">
+      <c r="AB9" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="AB9" s="11" t="s">
-        <v>50</v>
       </c>
       <c r="AC9" t="s" s="10">
         <v>31</v>
@@ -2903,7 +2890,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="true" autoPageBreaks="true"/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
@@ -3062,37 +3049,37 @@
         <v>31</v>
       </c>
       <c r="K2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="L2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="O2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="O2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="14" t="s">
+      <c r="U2" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="U2" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="V2" s="14" t="s">
         <v>31</v>
@@ -3124,46 +3111,46 @@
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s" s="6">
         <v>89</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="C3" t="s" s="6">
         <v>90</v>
       </c>
-      <c r="C3" t="s" s="6">
-        <v>91</v>
-      </c>
       <c r="D3" t="s" s="6">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s" s="6">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s" s="8">
         <v>45</v>
       </c>
       <c r="G3" t="s" s="7">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="7">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="I3" t="s" s="7">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="J3" t="s" s="8">
         <v>45</v>
       </c>
-      <c r="K3" s="12" t="s">
-        <v>95</v>
+      <c r="K3" t="s" s="12">
+        <v>31</v>
       </c>
       <c r="L3" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="M3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="N3" t="s" s="10">
-        <v>31</v>
+      <c r="M3" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="O3" t="s" s="10">
         <v>31</v>
@@ -3180,8 +3167,8 @@
       <c r="S3" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="T3" t="s" s="10">
-        <v>31</v>
+      <c r="T3" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="U3" t="s" s="10">
         <v>31</v>
@@ -3216,31 +3203,31 @@
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="6">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="6">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s" s="6">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s" s="6">
         <v>44</v>
       </c>
-      <c r="F4" t="s" s="8">
-        <v>45</v>
+      <c r="F4" t="s" s="9">
+        <v>96</v>
       </c>
       <c r="G4" t="s" s="7">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H4" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I4" t="s" s="7">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J4" t="s" s="8">
         <v>45</v>
@@ -3251,11 +3238,11 @@
       <c r="L4" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="M4" s="10" t="s">
-        <v>99</v>
+      <c r="M4" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="O4" t="s" s="10">
         <v>31</v>
@@ -3272,11 +3259,11 @@
       <c r="S4" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="T4" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="U4" t="s" s="10">
-        <v>31</v>
+      <c r="T4" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="V4" t="s" s="10">
         <v>31</v>
@@ -3308,64 +3295,64 @@
     </row>
     <row r="5" ht="33.0" customHeight="true">
       <c r="A5" t="s" s="6">
+        <v>99</v>
+      </c>
+      <c r="B5" t="s" s="6">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s" s="6">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s" s="6">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s" s="6">
+        <v>100</v>
+      </c>
+      <c r="F5" t="s" s="8">
+        <v>45</v>
+      </c>
+      <c r="G5" t="s" s="7">
         <v>101</v>
       </c>
-      <c r="B5" t="s" s="6">
+      <c r="H5" t="s" s="7">
+        <v>54</v>
+      </c>
+      <c r="I5" t="s" s="7">
         <v>102</v>
       </c>
-      <c r="C5" t="s" s="6">
-        <v>91</v>
-      </c>
-      <c r="D5" t="s" s="6">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s" s="6">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s" s="9">
+      <c r="J5" t="s" s="9">
         <v>103</v>
       </c>
-      <c r="G5" t="s" s="7">
+      <c r="K5" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="N5" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="O5" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="P5" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="Q5" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="R5" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="S5" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="T5" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="H5" t="s" s="7">
-        <v>55</v>
-      </c>
-      <c r="I5" t="s" s="7">
-        <v>104</v>
-      </c>
-      <c r="J5" t="s" s="8">
-        <v>45</v>
-      </c>
-      <c r="K5" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="L5" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M5" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="O5" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="P5" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Q5" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="R5" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="S5" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="T5" t="s" s="10">
-        <v>31</v>
       </c>
       <c r="U5" s="11" t="s">
         <v>105</v>
@@ -3395,98 +3382,6 @@
         <v>31</v>
       </c>
       <c r="AD5" t="s" s="10">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" ht="33.0" customHeight="true">
-      <c r="A6" t="s" s="6">
-        <v>106</v>
-      </c>
-      <c r="B6" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s" s="6">
-        <v>91</v>
-      </c>
-      <c r="D6" t="s" s="6">
-        <v>67</v>
-      </c>
-      <c r="E6" t="s" s="6">
-        <v>107</v>
-      </c>
-      <c r="F6" t="s" s="8">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s" s="7">
-        <v>108</v>
-      </c>
-      <c r="H6" t="s" s="7">
-        <v>55</v>
-      </c>
-      <c r="I6" t="s" s="7">
-        <v>109</v>
-      </c>
-      <c r="J6" t="s" s="9">
-        <v>110</v>
-      </c>
-      <c r="K6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="N6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="O6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="P6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Q6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="R6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="S6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="T6" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="U6" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="V6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="W6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="X6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Y6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="Z6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="AA6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AB6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AC6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AD6" t="s" s="10">
         <v>31</v>
       </c>
     </row>
@@ -3670,7 +3565,7 @@
         <v>31</v>
       </c>
       <c r="N2" s="14" t="s">
-        <v>31</v>
+        <v>106</v>
       </c>
       <c r="O2" s="14" t="s">
         <v>31</v>
@@ -3688,7 +3583,7 @@
         <v>31</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="U2" s="14" t="s">
         <v>31</v>
@@ -3723,19 +3618,19 @@
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s" s="6">
         <v>53</v>
-      </c>
-      <c r="E3" t="s" s="6">
-        <v>54</v>
       </c>
       <c r="F3" t="s" s="8">
         <v>45</v>
@@ -3744,10 +3639,10 @@
         <v>48</v>
       </c>
       <c r="H3" t="s" s="7">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="I3" t="s" s="7">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s" s="8">
         <v>45</v>
@@ -3761,8 +3656,8 @@
       <c r="M3" t="s" s="10">
         <v>31</v>
       </c>
-      <c r="N3" t="s" s="10">
-        <v>31</v>
+      <c r="N3" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="O3" t="s" s="10">
         <v>31</v>
@@ -3779,8 +3674,8 @@
       <c r="S3" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="T3" s="11" t="s">
-        <v>119</v>
+      <c r="T3" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="U3" t="s" s="10">
         <v>31</v>
@@ -3815,31 +3710,31 @@
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s" s="6">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s" s="6">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s" s="6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s" s="6">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F4" t="s" s="8">
         <v>45</v>
       </c>
       <c r="G4" t="s" s="7">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="H4" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I4" t="s" s="7">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="J4" t="s" s="8">
         <v>45</v>
@@ -3872,7 +3767,7 @@
         <v>31</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="U4" t="s" s="10">
         <v>31</v>
@@ -3917,7 +3812,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="true" autoPageBreaks="true"/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
@@ -4076,13 +3971,13 @@
         <v>31</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>31</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="N2" s="14" t="s">
         <v>31</v>
@@ -4103,13 +3998,13 @@
         <v>31</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="W2" s="14" t="s">
         <v>31</v>
@@ -4138,31 +4033,31 @@
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s" s="6">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s" s="6">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s" s="8">
         <v>45</v>
       </c>
       <c r="G3" t="s" s="7">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="H3" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I3" t="s" s="7">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J3" t="s" s="8">
         <v>45</v>
@@ -4174,7 +4069,7 @@
         <v>31</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="N3" t="s" s="10">
         <v>31</v>
@@ -4198,7 +4093,7 @@
         <v>31</v>
       </c>
       <c r="U3" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="V3" t="s" s="10">
         <v>31</v>
@@ -4230,67 +4125,67 @@
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s" s="6">
-        <v>138</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s" s="6">
         <v>132</v>
       </c>
       <c r="D4" t="s" s="6">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s" s="6">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s" s="8">
         <v>45</v>
       </c>
       <c r="G4" t="s" s="7">
+        <v>133</v>
+      </c>
+      <c r="H4" t="s" s="7">
+        <v>54</v>
+      </c>
+      <c r="I4" t="s" s="7">
+        <v>133</v>
+      </c>
+      <c r="J4" t="s" s="8">
+        <v>45</v>
+      </c>
+      <c r="K4" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="N4" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="O4" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="Q4" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="R4" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="S4" t="s" s="12">
+        <v>31</v>
+      </c>
+      <c r="T4" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="H4" t="s" s="7">
-        <v>55</v>
-      </c>
-      <c r="I4" t="s" s="7">
-        <v>139</v>
-      </c>
-      <c r="J4" t="s" s="9">
-        <v>140</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="L4" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N4" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="O4" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="P4" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Q4" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="R4" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="S4" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="T4" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="U4" t="s" s="10">
-        <v>31</v>
+      <c r="U4" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="V4" t="s" s="10">
         <v>31</v>
@@ -4322,31 +4217,31 @@
     </row>
     <row r="5" ht="33.0" customHeight="true">
       <c r="A5" t="s" s="6">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="6">
         <v>31</v>
       </c>
       <c r="C5" t="s" s="6">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s" s="6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s" s="6">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s" s="8">
         <v>45</v>
       </c>
       <c r="G5" t="s" s="7">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="H5" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I5" t="s" s="7">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="J5" t="s" s="8">
         <v>45</v>
@@ -4378,14 +4273,14 @@
       <c r="S5" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="T5" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="U5" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="V5" t="s" s="10">
-        <v>31</v>
+      <c r="T5" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>138</v>
       </c>
       <c r="W5" t="s" s="10">
         <v>31</v>
@@ -4409,98 +4304,6 @@
         <v>31</v>
       </c>
       <c r="AD5" t="s" s="10">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" ht="33.0" customHeight="true">
-      <c r="A6" t="s" s="6">
-        <v>106</v>
-      </c>
-      <c r="B6" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s" s="6">
-        <v>132</v>
-      </c>
-      <c r="D6" t="s" s="6">
-        <v>67</v>
-      </c>
-      <c r="E6" t="s" s="6">
-        <v>107</v>
-      </c>
-      <c r="F6" t="s" s="8">
-        <v>45</v>
-      </c>
-      <c r="G6" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="H6" t="s" s="7">
-        <v>55</v>
-      </c>
-      <c r="I6" t="s" s="7">
-        <v>146</v>
-      </c>
-      <c r="J6" t="s" s="8">
-        <v>45</v>
-      </c>
-      <c r="K6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="N6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="O6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="P6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Q6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="R6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="S6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="T6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="U6" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="V6" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="W6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="X6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Y6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="Z6" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="AA6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AB6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AC6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AD6" t="s" s="10">
         <v>31</v>
       </c>
     </row>
@@ -4516,7 +4319,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="true" autoPageBreaks="true"/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
@@ -4675,75 +4478,75 @@
         <v>31</v>
       </c>
       <c r="K2" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="W2" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="X2" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB2" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC2" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="L2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="14" t="s">
+      <c r="AD2" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="U2" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="V2" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="W2" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="X2" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA2" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB2" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD2" s="14" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B3" t="s" s="6">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s" s="6">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s" s="6">
         <v>43</v>
@@ -4758,10 +4561,10 @@
         <v>46</v>
       </c>
       <c r="H3" t="s" s="7">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="I3" t="s" s="7">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="J3" t="s" s="8">
         <v>45</v>
@@ -4773,7 +4576,7 @@
         <v>31</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="N3" t="s" s="10">
         <v>31</v>
@@ -4835,7 +4638,7 @@
         <v>41</v>
       </c>
       <c r="C4" t="s" s="6">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s" s="6">
         <v>43</v>
@@ -4850,7 +4653,7 @@
         <v>46</v>
       </c>
       <c r="H4" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I4" t="s" s="7">
         <v>46</v>
@@ -4865,10 +4668,10 @@
         <v>31</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="O4" t="s" s="10">
         <v>31</v>
@@ -4921,19 +4724,19 @@
     </row>
     <row r="5" ht="33.0" customHeight="true">
       <c r="A5" t="s" s="6">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s" s="6">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s" s="6">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s" s="6">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s" s="6">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F5" t="s" s="8">
         <v>45</v>
@@ -4942,16 +4745,16 @@
         <v>48</v>
       </c>
       <c r="H5" t="s" s="7">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="I5" t="s" s="7">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="J5" t="s" s="8">
         <v>45</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="L5" t="s" s="12">
         <v>31</v>
@@ -4977,8 +4780,8 @@
       <c r="S5" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="T5" s="11" t="s">
-        <v>64</v>
+      <c r="T5" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="U5" t="s" s="10">
         <v>31</v>
@@ -5013,37 +4816,37 @@
     </row>
     <row r="6" ht="33.0" customHeight="true">
       <c r="A6" t="s" s="6">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s" s="6">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s" s="6">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s" s="6">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s" s="6">
         <v>53</v>
       </c>
-      <c r="E6" t="s" s="6">
-        <v>176</v>
-      </c>
-      <c r="F6" t="s" s="9">
-        <v>103</v>
+      <c r="F6" t="s" s="8">
+        <v>45</v>
       </c>
       <c r="G6" t="s" s="7">
-        <v>177</v>
+        <v>46</v>
       </c>
       <c r="H6" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I6" t="s" s="7">
-        <v>177</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s" s="8">
         <v>45</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>178</v>
+      <c r="K6" t="s" s="12">
+        <v>31</v>
       </c>
       <c r="L6" t="s" s="12">
         <v>31</v>
@@ -5069,14 +4872,14 @@
       <c r="S6" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="T6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="U6" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="V6" t="s" s="10">
-        <v>31</v>
+      <c r="T6" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="V6" s="11" t="s">
+        <v>168</v>
       </c>
       <c r="W6" t="s" s="10">
         <v>31</v>
@@ -5105,19 +4908,19 @@
     </row>
     <row r="7" ht="33.0" customHeight="true">
       <c r="A7" t="s" s="6">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s" s="6">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s" s="6">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D7" t="s" s="6">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s" s="6">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s" s="8">
         <v>45</v>
@@ -5126,7 +4929,7 @@
         <v>46</v>
       </c>
       <c r="H7" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s" s="7">
         <v>46</v>
@@ -5161,20 +4964,20 @@
       <c r="S7" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="T7" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="U7" s="11" t="s">
-        <v>180</v>
+      <c r="T7" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="U7" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="W7" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="X7" t="s" s="10">
-        <v>31</v>
+        <v>83</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="Y7" t="s" s="12">
         <v>31</v>
@@ -5182,8 +4985,8 @@
       <c r="Z7" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="AA7" t="s" s="10">
-        <v>31</v>
+      <c r="AA7" s="11" t="s">
+        <v>169</v>
       </c>
       <c r="AB7" t="s" s="10">
         <v>31</v>
@@ -5197,28 +5000,28 @@
     </row>
     <row r="8" ht="33.0" customHeight="true">
       <c r="A8" t="s" s="6">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s" s="6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s" s="6">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s" s="6">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s" s="6">
-        <v>62</v>
-      </c>
-      <c r="F8" t="s" s="8">
-        <v>45</v>
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="9">
+        <v>96</v>
       </c>
       <c r="G8" t="s" s="7">
         <v>46</v>
       </c>
       <c r="H8" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I8" t="s" s="7">
         <v>46</v>
@@ -5256,17 +5059,17 @@
       <c r="T8" t="s" s="10">
         <v>31</v>
       </c>
-      <c r="U8" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="V8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="W8" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="X8" s="10" t="s">
-        <v>56</v>
+      <c r="U8" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="V8" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="W8" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="X8" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="Y8" t="s" s="12">
         <v>31</v>
@@ -5275,10 +5078,10 @@
         <v>31</v>
       </c>
       <c r="AA8" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB8" t="s" s="10">
-        <v>31</v>
+        <v>168</v>
+      </c>
+      <c r="AB8" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="AC8" t="s" s="10">
         <v>31</v>
@@ -5289,28 +5092,28 @@
     </row>
     <row r="9" ht="33.0" customHeight="true">
       <c r="A9" t="s" s="6">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s" s="6">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s" s="6">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D9" t="s" s="6">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s" s="6">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s" s="9">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G9" t="s" s="7">
         <v>46</v>
       </c>
       <c r="H9" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I9" t="s" s="7">
         <v>46</v>
@@ -5348,14 +5151,14 @@
       <c r="T9" t="s" s="10">
         <v>31</v>
       </c>
-      <c r="U9" s="10" t="s">
-        <v>178</v>
+      <c r="U9" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="V9" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="W9" t="s" s="10">
-        <v>31</v>
+        <v>71</v>
+      </c>
+      <c r="W9" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="X9" t="s" s="10">
         <v>31</v>
@@ -5366,14 +5169,14 @@
       <c r="Z9" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="AA9" s="11" t="s">
-        <v>96</v>
+      <c r="AA9" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="AB9" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="AC9" t="s" s="10">
-        <v>31</v>
+        <v>168</v>
+      </c>
+      <c r="AC9" s="11" t="s">
+        <v>172</v>
       </c>
       <c r="AD9" t="s" s="10">
         <v>31</v>
@@ -5381,28 +5184,28 @@
     </row>
     <row r="10" ht="33.0" customHeight="true">
       <c r="A10" t="s" s="6">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s" s="6">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s" s="6">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D10" t="s" s="6">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s" s="6">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s" s="9">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G10" t="s" s="7">
         <v>46</v>
       </c>
       <c r="H10" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s" s="7">
         <v>46</v>
@@ -5443,14 +5246,14 @@
       <c r="U10" t="s" s="10">
         <v>31</v>
       </c>
-      <c r="V10" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="W10" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="X10" t="s" s="10">
-        <v>31</v>
+      <c r="V10" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="W10" t="s" s="10">
+        <v>31</v>
+      </c>
+      <c r="X10" s="10" t="s">
+        <v>173</v>
       </c>
       <c r="Y10" t="s" s="12">
         <v>31</v>
@@ -5458,46 +5261,46 @@
       <c r="Z10" t="s" s="12">
         <v>31</v>
       </c>
-      <c r="AA10" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AB10" s="11" t="s">
-        <v>96</v>
+      <c r="AA10" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB10" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="AC10" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD10" t="s" s="10">
-        <v>31</v>
+        <v>168</v>
+      </c>
+      <c r="AD10" s="11" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="11" ht="33.0" customHeight="true">
       <c r="A11" t="s" s="6">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s" s="6">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s" s="6">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s" s="6">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s" s="6">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s" s="9">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G11" t="s" s="7">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s" s="7">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s" s="8">
         <v>45</v>
@@ -5541,8 +5344,8 @@
       <c r="W11" t="s" s="10">
         <v>31</v>
       </c>
-      <c r="X11" s="10" t="s">
-        <v>183</v>
+      <c r="X11" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="Y11" t="s" s="12">
         <v>31</v>
@@ -5551,108 +5354,16 @@
         <v>31</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="AB11" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AC11" s="11" t="s">
-        <v>96</v>
+        <v>166</v>
+      </c>
+      <c r="AB11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AC11" t="s" s="10">
+        <v>31</v>
       </c>
       <c r="AD11" s="11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" ht="33.0" customHeight="true">
-      <c r="A12" t="s" s="6">
-        <v>77</v>
-      </c>
-      <c r="B12" t="s" s="6">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s" s="6">
-        <v>162</v>
-      </c>
-      <c r="D12" t="s" s="6">
-        <v>79</v>
-      </c>
-      <c r="E12" t="s" s="6">
-        <v>80</v>
-      </c>
-      <c r="F12" t="s" s="9">
-        <v>103</v>
-      </c>
-      <c r="G12" t="s" s="7">
-        <v>81</v>
-      </c>
-      <c r="H12" t="s" s="7">
-        <v>55</v>
-      </c>
-      <c r="I12" t="s" s="7">
-        <v>81</v>
-      </c>
-      <c r="J12" t="s" s="8">
-        <v>45</v>
-      </c>
-      <c r="K12" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="L12" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="M12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="N12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="O12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="P12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Q12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="R12" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="S12" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="T12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="U12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="V12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="W12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="X12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="Y12" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="Z12" t="s" s="12">
-        <v>31</v>
-      </c>
-      <c r="AA12" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB12" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="10">
-        <v>31</v>
-      </c>
-      <c r="AD12" s="11" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/code/アラジン入力用配台計画/アラジン入力用_配台計画.xlsx
+++ b/code/アラジン入力用配台計画/アラジン入力用_配台計画.xlsx
@@ -13,22 +13,22 @@
     <sheet name="2021 熱融着機　湖南" r:id="rId7" sheetId="5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'2012 EC機　湖南'!$A$1:$AC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">'2012 EC機　湖南'!$A$1:$AB$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'2012 EC機　湖南'!$A:$J,'2012 EC機　湖南'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">'2014 SEC機　湖南'!$A$1:$AC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">'2014 SEC機　湖南'!$A$1:$AB$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'2014 SEC機　湖南'!$A:$J,'2014 SEC機　湖南'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">'2016 エンボス　湖南'!$A$1:$AC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="true">'2016 エンボス　湖南'!$A$1:$AB$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'2016 エンボス　湖南'!$A:$J,'2016 エンボス　湖南'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="true">'2013 スリット機1　湖南'!$A$1:$AC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="true">'2013 スリット機1　湖南'!$A$1:$AB$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'2013 スリット機1　湖南'!$A:$J,'2013 スリット機1　湖南'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="true">'2021 熱融着機　湖南'!$A$1:$AC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="true">'2021 熱融着機　湖南'!$A$1:$AB$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'2021 熱融着機　湖南'!$A:$J,'2021 熱融着機　湖南'!$1:$2</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="155">
   <si>
     <t>依頼NO</t>
   </si>
@@ -58,10 +58,6 @@
   </si>
   <si>
     <t>数量チェック</t>
-  </si>
-  <si>
-    <t>8/8
-(土)</t>
   </si>
   <si>
     <t>8/9
@@ -327,7 +323,7 @@
     <t>EC</t>
   </si>
   <si>
-    <t>2026/08/06</t>
+    <t>2026-08-06</t>
   </si>
   <si>
     <t>8/18</t>
@@ -371,7 +367,7 @@
     <t>190991R</t>
   </si>
   <si>
-    <t>2026/08/07</t>
+    <t>2026-08-07</t>
   </si>
   <si>
     <t>8/21</t>
@@ -426,7 +422,7 @@
     <t>190996M</t>
   </si>
   <si>
-    <t>2026/08/17</t>
+    <t>2026-08-17</t>
   </si>
   <si>
     <t>W8-9</t>
@@ -435,7 +431,7 @@
     <t>190997H</t>
   </si>
   <si>
-    <t>2026/08/18</t>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t>8/25</t>
@@ -487,7 +483,7 @@
     <t>190994Y</t>
   </si>
   <si>
-    <t>2026/08/19</t>
+    <t>2026-08-19</t>
   </si>
   <si>
     <t>W8-12</t>
@@ -505,7 +501,7 @@
     <t>191293B</t>
   </si>
   <si>
-    <t>2026/08/20</t>
+    <t>2026-08-20</t>
   </si>
   <si>
     <t>8/27</t>
@@ -1027,7 +1023,7 @@
     <t>スリット</t>
   </si>
   <si>
-    <t>2026/08/10</t>
+    <t>2026-08-10</t>
   </si>
   <si>
     <t>200</t>
@@ -1723,7 +1719,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="true" autoPageBreaks="true"/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AB9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
@@ -1754,7 +1750,6 @@
     <col min="26" max="26" width="16.80078125" customWidth="true"/>
     <col min="27" max="27" width="16.80078125" customWidth="true"/>
     <col min="28" max="28" width="16.80078125" customWidth="true"/>
-    <col min="29" max="29" width="16.80078125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="true">
@@ -1791,7 +1786,7 @@
       <c r="K1" t="s" s="5">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="4">
+      <c r="L1" t="s" s="2">
         <v>11</v>
       </c>
       <c r="M1" t="s" s="2">
@@ -1806,13 +1801,13 @@
       <c r="P1" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="Q1" t="s" s="2">
+      <c r="Q1" t="s" s="3">
         <v>16</v>
       </c>
-      <c r="R1" t="s" s="3">
+      <c r="R1" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="4">
+      <c r="S1" t="s" s="2">
         <v>18</v>
       </c>
       <c r="T1" t="s" s="2">
@@ -1827,13 +1822,13 @@
       <c r="W1" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="X1" t="s" s="2">
+      <c r="X1" t="s" s="3">
         <v>23</v>
       </c>
-      <c r="Y1" t="s" s="3">
+      <c r="Y1" t="s" s="4">
         <v>24</v>
       </c>
-      <c r="Z1" t="s" s="4">
+      <c r="Z1" t="s" s="2">
         <v>25</v>
       </c>
       <c r="AA1" t="s" s="2">
@@ -1841,68 +1836,65 @@
       </c>
       <c r="AB1" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="AC1" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="true">
       <c r="A2" t="s" s="13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>30</v>
       </c>
       <c r="M2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="14" t="s">
         <v>31</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="T2" s="14" t="s">
         <v>32</v>
@@ -1917,649 +1909,625 @@
         <v>35</v>
       </c>
       <c r="X2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="14" t="s">
         <v>36</v>
-      </c>
-      <c r="Y2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="AA2" s="14" t="s">
         <v>37</v>
       </c>
       <c r="AB2" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s" s="6">
         <v>39</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="C3" t="s" s="6">
         <v>40</v>
       </c>
-      <c r="C3" t="s" s="6">
+      <c r="D3" t="s" s="6">
         <v>41</v>
       </c>
-      <c r="D3" t="s" s="6">
+      <c r="E3" t="s" s="6">
         <v>42</v>
       </c>
-      <c r="E3" t="s" s="6">
+      <c r="F3" t="s" s="8">
         <v>43</v>
       </c>
-      <c r="F3" t="s" s="8">
+      <c r="G3" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G3" t="s" s="7">
+      <c r="H3" t="s" s="7">
         <v>45</v>
       </c>
-      <c r="H3" t="s" s="7">
+      <c r="I3" t="s" s="7">
         <v>46</v>
       </c>
-      <c r="I3" t="s" s="7">
+      <c r="J3" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="J3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>48</v>
+      <c r="M3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="N3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Q3" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="R3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="S3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="T3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X3" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z3" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s" s="6">
         <v>49</v>
       </c>
-      <c r="B4" t="s" s="6">
+      <c r="C4" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s" s="6">
         <v>50</v>
       </c>
-      <c r="C4" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s" s="6">
+      <c r="E4" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="E4" t="s" s="6">
+      <c r="F4" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="H4" t="s" s="7">
         <v>52</v>
       </c>
-      <c r="F4" t="s" s="8">
+      <c r="I4" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G4" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="H4" t="s" s="7">
+      <c r="J4" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I4" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="J4" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T4" s="10" t="s">
+      <c r="T4" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="U4" s="11" t="s">
-        <v>55</v>
+      <c r="U4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="V4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X4" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z4" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="33.0" customHeight="true">
       <c r="A5" t="s" s="6">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s" s="6">
         <v>56</v>
       </c>
-      <c r="B5" t="s" s="6">
+      <c r="C5" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s" s="6">
         <v>57</v>
       </c>
-      <c r="C5" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D5" t="s" s="6">
-        <v>58</v>
-      </c>
       <c r="E5" t="s" s="6">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s" s="7">
         <v>52</v>
       </c>
-      <c r="F5" t="s" s="8">
+      <c r="I5" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G5" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s" s="7">
+      <c r="J5" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T5" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I5" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="J5" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="U5" s="10" t="s">
+      <c r="U5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="V5" s="11" t="s">
-        <v>55</v>
+      <c r="V5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="W5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X5" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z5" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="33.0" customHeight="true">
       <c r="A6" t="s" s="6">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s" s="6">
         <v>59</v>
       </c>
-      <c r="B6" t="s" s="6">
+      <c r="C6" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s" s="6">
         <v>60</v>
       </c>
-      <c r="C6" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s" s="6">
+      <c r="E6" t="s" s="6">
         <v>61</v>
       </c>
-      <c r="E6" t="s" s="6">
+      <c r="F6" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q6" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R6" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T6" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="F6" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G6" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="H6" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I6" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="J6" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M6" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N6" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O6" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q6" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T6" t="s" s="10">
-        <v>30</v>
       </c>
       <c r="U6" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="V6" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="W6" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="X6" t="s" s="10">
-        <v>30</v>
+      <c r="V6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="W6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="X6" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z6" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z6" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB6" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="33.0" customHeight="true">
       <c r="A7" t="s" s="6">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s" s="6">
         <v>65</v>
       </c>
-      <c r="B7" t="s" s="6">
+      <c r="C7" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s" s="6">
         <v>66</v>
       </c>
-      <c r="C7" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D7" t="s" s="6">
-        <v>67</v>
-      </c>
       <c r="E7" t="s" s="6">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G7" t="s" s="7">
-        <v>45</v>
-      </c>
       <c r="H7" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I7" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K7" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q7" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R7" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="U7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I7" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="J7" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="U7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="V7" s="10" t="s">
+      <c r="V7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="W7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="W7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X7" s="11" t="s">
-        <v>55</v>
+      <c r="X7" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z7" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z7" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA7" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC7" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="33.0" customHeight="true">
       <c r="A8" t="s" s="6">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s" s="6">
         <v>68</v>
       </c>
-      <c r="B8" t="s" s="6">
+      <c r="C8" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s" s="6">
+        <v>66</v>
+      </c>
+      <c r="E8" t="s" s="6">
         <v>69</v>
       </c>
-      <c r="C8" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s" s="6">
-        <v>67</v>
-      </c>
-      <c r="E8" t="s" s="6">
-        <v>70</v>
-      </c>
       <c r="F8" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G8" t="s" s="7">
-        <v>45</v>
-      </c>
       <c r="H8" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I8" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="U8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="V8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I8" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="J8" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="U8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="V8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="W8" s="10" t="s">
+      <c r="W8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="X8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="Y8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="Z8" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="X8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Y8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="AA8" s="11" t="s">
-        <v>55</v>
+      <c r="AA8" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AB8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC8" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="33.0" customHeight="true">
       <c r="A9" t="s" s="6">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s" s="6">
         <v>71</v>
       </c>
-      <c r="B9" t="s" s="6">
+      <c r="C9" t="s" s="6">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s" s="6">
         <v>72</v>
       </c>
-      <c r="C9" t="s" s="6">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s" s="6">
+      <c r="E9" t="s" s="6">
         <v>73</v>
       </c>
-      <c r="E9" t="s" s="6">
+      <c r="F9" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s" s="7">
         <v>74</v>
       </c>
-      <c r="F9" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s" s="7">
+      <c r="H9" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I9" t="s" s="7">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K9" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q9" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R9" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="U9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="V9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="W9" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H9" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I9" t="s" s="7">
-        <v>75</v>
-      </c>
-      <c r="J9" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="U9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="V9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="W9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X9" s="10" t="s">
+      <c r="X9" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="Y9" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="Z9" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="AA9" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Y9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="AA9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AB9" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC9" t="s" s="10">
-        <v>30</v>
+      <c r="AB9" t="s" s="10">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC1"/>
+  <autoFilter ref="A1:AB1"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.25" right="0.25" top="0.75"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="2" fitToHeight="0"/>
 </worksheet>
@@ -2570,7 +2538,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="true" autoPageBreaks="true"/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
@@ -2601,7 +2569,6 @@
     <col min="26" max="26" width="16.80078125" customWidth="true"/>
     <col min="27" max="27" width="16.80078125" customWidth="true"/>
     <col min="28" max="28" width="16.80078125" customWidth="true"/>
-    <col min="29" max="29" width="16.80078125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="true">
@@ -2638,7 +2605,7 @@
       <c r="K1" t="s" s="5">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="4">
+      <c r="L1" t="s" s="2">
         <v>11</v>
       </c>
       <c r="M1" t="s" s="2">
@@ -2653,13 +2620,13 @@
       <c r="P1" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="Q1" t="s" s="2">
+      <c r="Q1" t="s" s="3">
         <v>16</v>
       </c>
-      <c r="R1" t="s" s="3">
+      <c r="R1" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="4">
+      <c r="S1" t="s" s="2">
         <v>18</v>
       </c>
       <c r="T1" t="s" s="2">
@@ -2674,13 +2641,13 @@
       <c r="W1" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="X1" t="s" s="2">
+      <c r="X1" t="s" s="3">
         <v>23</v>
       </c>
-      <c r="Y1" t="s" s="3">
+      <c r="Y1" t="s" s="4">
         <v>24</v>
       </c>
-      <c r="Z1" t="s" s="4">
+      <c r="Z1" t="s" s="2">
         <v>25</v>
       </c>
       <c r="AA1" t="s" s="2">
@@ -2688,369 +2655,354 @@
       </c>
       <c r="AB1" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="AC1" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="true">
       <c r="A2" t="s" s="13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>78</v>
       </c>
       <c r="N2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="14" t="s">
         <v>79</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="T2" s="14" t="s">
         <v>80</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s" s="6">
         <v>82</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="C3" t="s" s="6">
         <v>83</v>
       </c>
-      <c r="C3" t="s" s="6">
+      <c r="D3" t="s" s="6">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s" s="6">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s" s="7">
         <v>84</v>
       </c>
-      <c r="D3" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s" s="6">
+      <c r="H3" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I3" t="s" s="7">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s" s="8">
         <v>43</v>
       </c>
-      <c r="F3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s" s="7">
+      <c r="K3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L3" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="H3" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s" s="7">
-        <v>85</v>
-      </c>
-      <c r="J3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s" s="12">
-        <v>30</v>
       </c>
       <c r="M3" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S3" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="O3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>88</v>
+      <c r="T3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="U3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X3" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z3" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
+        <v>88</v>
+      </c>
+      <c r="B4" t="s" s="6">
         <v>89</v>
       </c>
-      <c r="B4" t="s" s="6">
+      <c r="C4" t="s" s="6">
+        <v>83</v>
+      </c>
+      <c r="D4" t="s" s="6">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s" s="6">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s" s="9">
         <v>90</v>
       </c>
-      <c r="C4" t="s" s="6">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="E4" t="s" s="6">
+      <c r="G4" t="s" s="7">
+        <v>91</v>
+      </c>
+      <c r="H4" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s" s="7">
+        <v>91</v>
+      </c>
+      <c r="J4" t="s" s="8">
         <v>43</v>
       </c>
-      <c r="F4" t="s" s="9">
-        <v>91</v>
-      </c>
-      <c r="G4" t="s" s="7">
+      <c r="K4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="N4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S4" s="11" t="s">
         <v>92</v>
-      </c>
-      <c r="H4" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I4" t="s" s="7">
-        <v>92</v>
-      </c>
-      <c r="J4" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="O4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s" s="12">
-        <v>30</v>
       </c>
       <c r="T4" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="U4" s="11" t="s">
-        <v>94</v>
+      <c r="U4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="V4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X4" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z4" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="33.0" customHeight="true">
       <c r="A5" t="s" s="6">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s" s="6">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s" s="6">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s" s="6">
+        <v>57</v>
+      </c>
+      <c r="E5" t="s" s="6">
         <v>95</v>
       </c>
-      <c r="B5" t="s" s="6">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s" s="6">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s" s="6">
-        <v>58</v>
-      </c>
-      <c r="E5" t="s" s="6">
+      <c r="F5" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s" s="7">
         <v>96</v>
       </c>
-      <c r="F5" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s" s="7">
+      <c r="H5" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s" s="7">
         <v>97</v>
       </c>
-      <c r="H5" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I5" t="s" s="7">
+      <c r="J5" t="s" s="9">
         <v>98</v>
       </c>
-      <c r="J5" t="s" s="9">
+      <c r="K5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S5" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="K5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T5" s="10" t="s">
+      <c r="T5" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="U5" s="11" t="s">
-        <v>101</v>
+      <c r="U5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="V5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X5" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z5" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC1"/>
+  <autoFilter ref="A1:AB1"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.25" right="0.25" top="0.75"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="2" fitToHeight="0"/>
 </worksheet>
@@ -3061,7 +3013,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="true" autoPageBreaks="true"/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
@@ -3092,7 +3044,6 @@
     <col min="26" max="26" width="16.80078125" customWidth="true"/>
     <col min="27" max="27" width="16.80078125" customWidth="true"/>
     <col min="28" max="28" width="16.80078125" customWidth="true"/>
-    <col min="29" max="29" width="16.80078125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="true">
@@ -3129,7 +3080,7 @@
       <c r="K1" t="s" s="5">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="4">
+      <c r="L1" t="s" s="2">
         <v>11</v>
       </c>
       <c r="M1" t="s" s="2">
@@ -3144,13 +3095,13 @@
       <c r="P1" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="Q1" t="s" s="2">
+      <c r="Q1" t="s" s="3">
         <v>16</v>
       </c>
-      <c r="R1" t="s" s="3">
+      <c r="R1" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="4">
+      <c r="S1" t="s" s="2">
         <v>18</v>
       </c>
       <c r="T1" t="s" s="2">
@@ -3165,13 +3116,13 @@
       <c r="W1" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="X1" t="s" s="2">
+      <c r="X1" t="s" s="3">
         <v>23</v>
       </c>
-      <c r="Y1" t="s" s="3">
+      <c r="Y1" t="s" s="4">
         <v>24</v>
       </c>
-      <c r="Z1" t="s" s="4">
+      <c r="Z1" t="s" s="2">
         <v>25</v>
       </c>
       <c r="AA1" t="s" s="2">
@@ -3179,280 +3130,268 @@
       </c>
       <c r="AB1" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="AC1" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="true">
       <c r="A2" t="s" s="13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>30</v>
+        <v>101</v>
       </c>
       <c r="N2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>30</v>
-      </c>
       <c r="T2" s="14" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
+        <v>103</v>
+      </c>
+      <c r="B3" t="s" s="6">
         <v>104</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="C3" t="s" s="6">
         <v>105</v>
       </c>
-      <c r="C3" t="s" s="6">
+      <c r="D3" t="s" s="6">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s" s="6">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="H3" t="s" s="7">
         <v>106</v>
       </c>
-      <c r="D3" t="s" s="6">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s" s="6">
-        <v>52</v>
-      </c>
-      <c r="F3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s" s="7">
-        <v>47</v>
-      </c>
-      <c r="H3" t="s" s="7">
+      <c r="I3" t="s" s="7">
         <v>107</v>
       </c>
-      <c r="I3" t="s" s="7">
+      <c r="J3" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="J3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S3" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="O3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T3" s="10" t="s">
-        <v>110</v>
+      <c r="T3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="U3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X3" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z3" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s" s="6">
         <v>111</v>
       </c>
-      <c r="B4" t="s" s="6">
+      <c r="C4" t="s" s="6">
+        <v>105</v>
+      </c>
+      <c r="D4" t="s" s="6">
+        <v>57</v>
+      </c>
+      <c r="E4" t="s" s="6">
         <v>112</v>
       </c>
-      <c r="C4" t="s" s="6">
-        <v>106</v>
-      </c>
-      <c r="D4" t="s" s="6">
-        <v>58</v>
-      </c>
-      <c r="E4" t="s" s="6">
+      <c r="F4" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s" s="7">
         <v>113</v>
       </c>
-      <c r="F4" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s" s="7">
+      <c r="H4" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s" s="7">
+        <v>113</v>
+      </c>
+      <c r="J4" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S4" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="H4" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I4" t="s" s="7">
-        <v>114</v>
-      </c>
-      <c r="J4" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T4" s="10" t="s">
-        <v>115</v>
+      <c r="T4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="U4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X4" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z4" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC1"/>
+  <autoFilter ref="A1:AB1"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.25" right="0.25" top="0.75"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="2" fitToHeight="0"/>
 </worksheet>
@@ -3463,7 +3402,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="true" autoPageBreaks="true"/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
@@ -3494,7 +3433,6 @@
     <col min="26" max="26" width="16.80078125" customWidth="true"/>
     <col min="27" max="27" width="16.80078125" customWidth="true"/>
     <col min="28" max="28" width="16.80078125" customWidth="true"/>
-    <col min="29" max="29" width="16.80078125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="true">
@@ -3531,7 +3469,7 @@
       <c r="K1" t="s" s="5">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="4">
+      <c r="L1" t="s" s="2">
         <v>11</v>
       </c>
       <c r="M1" t="s" s="2">
@@ -3546,13 +3484,13 @@
       <c r="P1" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="Q1" t="s" s="2">
+      <c r="Q1" t="s" s="3">
         <v>16</v>
       </c>
-      <c r="R1" t="s" s="3">
+      <c r="R1" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="4">
+      <c r="S1" t="s" s="2">
         <v>18</v>
       </c>
       <c r="T1" t="s" s="2">
@@ -3567,13 +3505,13 @@
       <c r="W1" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="X1" t="s" s="2">
+      <c r="X1" t="s" s="3">
         <v>23</v>
       </c>
-      <c r="Y1" t="s" s="3">
+      <c r="Y1" t="s" s="4">
         <v>24</v>
       </c>
-      <c r="Z1" t="s" s="4">
+      <c r="Z1" t="s" s="2">
         <v>25</v>
       </c>
       <c r="AA1" t="s" s="2">
@@ -3581,369 +3519,354 @@
       </c>
       <c r="AB1" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="AC1" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="true">
       <c r="A2" t="s" s="13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="M2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="T2" s="14" t="s">
         <v>117</v>
       </c>
       <c r="U2" s="14" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s" s="6">
         <v>119</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="C3" t="s" s="6">
         <v>120</v>
       </c>
-      <c r="C3" t="s" s="6">
+      <c r="D3" t="s" s="6">
         <v>121</v>
       </c>
-      <c r="D3" t="s" s="6">
+      <c r="E3" t="s" s="6">
+        <v>112</v>
+      </c>
+      <c r="F3" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s" s="7">
         <v>122</v>
       </c>
-      <c r="E3" t="s" s="6">
-        <v>113</v>
-      </c>
-      <c r="F3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s" s="7">
+      <c r="H3" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I3" t="s" s="7">
+        <v>122</v>
+      </c>
+      <c r="J3" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L3" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="H3" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s" s="7">
-        <v>123</v>
-      </c>
-      <c r="J3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S3" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T3" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="N3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="U3" s="10" t="s">
-        <v>125</v>
+      <c r="U3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="V3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X3" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z3" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
+        <v>125</v>
+      </c>
+      <c r="B4" t="s" s="6">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s" s="6">
         <v>126</v>
       </c>
-      <c r="B4" t="s" s="6">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s" s="6">
+      <c r="D4" t="s" s="6">
+        <v>57</v>
+      </c>
+      <c r="E4" t="s" s="6">
+        <v>95</v>
+      </c>
+      <c r="F4" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s" s="7">
         <v>127</v>
       </c>
-      <c r="D4" t="s" s="6">
-        <v>58</v>
-      </c>
-      <c r="E4" t="s" s="6">
-        <v>96</v>
-      </c>
-      <c r="F4" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G4" t="s" s="7">
+      <c r="H4" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s" s="7">
+        <v>127</v>
+      </c>
+      <c r="J4" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R4" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S4" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="H4" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I4" t="s" s="7">
-        <v>128</v>
-      </c>
-      <c r="J4" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T4" s="11" t="s">
+      <c r="T4" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="U4" s="10" t="s">
-        <v>130</v>
+      <c r="U4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="V4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X4" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z4" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="33.0" customHeight="true">
       <c r="A5" t="s" s="6">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s" s="6">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s" s="6">
+        <v>120</v>
+      </c>
+      <c r="D5" t="s" s="6">
+        <v>57</v>
+      </c>
+      <c r="E5" t="s" s="6">
         <v>95</v>
       </c>
-      <c r="B5" t="s" s="6">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s" s="6">
-        <v>121</v>
-      </c>
-      <c r="D5" t="s" s="6">
-        <v>58</v>
-      </c>
-      <c r="E5" t="s" s="6">
-        <v>96</v>
-      </c>
       <c r="F5" t="s" s="8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s" s="7">
+        <v>130</v>
+      </c>
+      <c r="H5" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s" s="7">
+        <v>130</v>
+      </c>
+      <c r="J5" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R5" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S5" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T5" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="H5" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I5" t="s" s="7">
-        <v>131</v>
-      </c>
-      <c r="J5" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="U5" s="10" t="s">
-        <v>132</v>
+      <c r="U5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="V5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X5" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z5" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC1"/>
+  <autoFilter ref="A1:AB1"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.25" right="0.25" top="0.75"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="2" fitToHeight="0"/>
 </worksheet>
@@ -3954,7 +3877,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="true" autoPageBreaks="true"/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="14.0" customWidth="true"/>
@@ -3985,7 +3908,6 @@
     <col min="26" max="26" width="16.80078125" customWidth="true"/>
     <col min="27" max="27" width="16.80078125" customWidth="true"/>
     <col min="28" max="28" width="16.80078125" customWidth="true"/>
-    <col min="29" max="29" width="16.80078125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.0" customHeight="true">
@@ -4022,7 +3944,7 @@
       <c r="K1" t="s" s="5">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="4">
+      <c r="L1" t="s" s="2">
         <v>11</v>
       </c>
       <c r="M1" t="s" s="2">
@@ -4037,13 +3959,13 @@
       <c r="P1" t="s" s="2">
         <v>15</v>
       </c>
-      <c r="Q1" t="s" s="2">
+      <c r="Q1" t="s" s="3">
         <v>16</v>
       </c>
-      <c r="R1" t="s" s="3">
+      <c r="R1" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="S1" t="s" s="4">
+      <c r="S1" t="s" s="2">
         <v>18</v>
       </c>
       <c r="T1" t="s" s="2">
@@ -4058,13 +3980,13 @@
       <c r="W1" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="X1" t="s" s="2">
+      <c r="X1" t="s" s="3">
         <v>23</v>
       </c>
-      <c r="Y1" t="s" s="3">
+      <c r="Y1" t="s" s="4">
         <v>24</v>
       </c>
-      <c r="Z1" t="s" s="4">
+      <c r="Z1" t="s" s="2">
         <v>25</v>
       </c>
       <c r="AA1" t="s" s="2">
@@ -4072,68 +3994,65 @@
       </c>
       <c r="AB1" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="AC1" t="s" s="2">
-        <v>28</v>
       </c>
     </row>
     <row r="2" ht="33.0" customHeight="true">
       <c r="A2" t="s" s="13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s" s="13">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>133</v>
       </c>
       <c r="N2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="14" t="s">
         <v>134</v>
-      </c>
-      <c r="O2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="T2" s="14" t="s">
         <v>135</v>
@@ -4148,738 +4067,711 @@
         <v>138</v>
       </c>
       <c r="X2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z2" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="Y2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="14" t="s">
-        <v>30</v>
-      </c>
       <c r="AA2" s="14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AB2" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="33.0" customHeight="true">
       <c r="A3" t="s" s="6">
+        <v>140</v>
+      </c>
+      <c r="B3" t="s" s="6">
         <v>141</v>
       </c>
-      <c r="B3" t="s" s="6">
+      <c r="C3" t="s" s="6">
         <v>142</v>
       </c>
-      <c r="C3" t="s" s="6">
+      <c r="D3" t="s" s="6">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s" s="6">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G3" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="H3" t="s" s="7">
         <v>143</v>
       </c>
-      <c r="D3" t="s" s="6">
-        <v>42</v>
-      </c>
-      <c r="E3" t="s" s="6">
+      <c r="I3" t="s" s="7">
+        <v>144</v>
+      </c>
+      <c r="J3" t="s" s="8">
         <v>43</v>
       </c>
-      <c r="F3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G3" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="H3" t="s" s="7">
-        <v>144</v>
-      </c>
-      <c r="I3" t="s" s="7">
+      <c r="K3" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L3" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="J3" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>146</v>
+      <c r="M3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="N3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Q3" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="R3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="S3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="T3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X3" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y3" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z3" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z3" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC3" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="33.0" customHeight="true">
       <c r="A4" t="s" s="6">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s" s="6">
         <v>39</v>
       </c>
-      <c r="B4" t="s" s="6">
-        <v>40</v>
-      </c>
       <c r="C4" t="s" s="6">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s" s="6">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s" s="6">
         <v>42</v>
       </c>
-      <c r="E4" t="s" s="6">
+      <c r="F4" t="s" s="8">
         <v>43</v>
       </c>
-      <c r="F4" t="s" s="8">
+      <c r="G4" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G4" t="s" s="7">
-        <v>45</v>
-      </c>
       <c r="H4" t="s" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I4" t="s" s="7">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J4" t="s" s="8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>146</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="N4" s="11" t="s">
-        <v>148</v>
+      <c r="N4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="O4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Q4" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="R4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="S4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="T4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X4" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y4" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z4" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z4" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB4" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC4" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="33.0" customHeight="true">
       <c r="A5" t="s" s="6">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s" s="6">
         <v>49</v>
       </c>
-      <c r="B5" t="s" s="6">
+      <c r="C5" t="s" s="6">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s" s="6">
         <v>50</v>
       </c>
-      <c r="C5" t="s" s="6">
-        <v>143</v>
-      </c>
-      <c r="D5" t="s" s="6">
+      <c r="E5" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="E5" t="s" s="6">
+      <c r="F5" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s" s="7">
         <v>52</v>
       </c>
-      <c r="F5" t="s" s="8">
+      <c r="I5" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G5" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="H5" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I5" t="s" s="7">
-        <v>45</v>
-      </c>
       <c r="J5" t="s" s="8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L5" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="L5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="M5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="R5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S5" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="T5" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="U5" s="10" t="s">
+      <c r="U5" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="V5" s="11" t="s">
-        <v>151</v>
+      <c r="V5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="W5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X5" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y5" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z5" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z5" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB5" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC5" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="33.0" customHeight="true">
       <c r="A6" t="s" s="6">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s" s="6">
         <v>56</v>
       </c>
-      <c r="B6" t="s" s="6">
+      <c r="C6" t="s" s="6">
+        <v>142</v>
+      </c>
+      <c r="D6" t="s" s="6">
         <v>57</v>
       </c>
-      <c r="C6" t="s" s="6">
-        <v>143</v>
-      </c>
-      <c r="D6" t="s" s="6">
-        <v>58</v>
-      </c>
       <c r="E6" t="s" s="6">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="H6" t="s" s="7">
         <v>52</v>
       </c>
-      <c r="F6" t="s" s="8">
+      <c r="I6" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G6" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="H6" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I6" t="s" s="7">
-        <v>45</v>
-      </c>
       <c r="J6" t="s" s="8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L6" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="L6" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="M6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P6" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Q6" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="R6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="S6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T6" s="10" t="s">
+        <v>151</v>
       </c>
       <c r="U6" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="V6" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="W6" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="X6" t="s" s="10">
-        <v>30</v>
+      <c r="V6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="W6" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="X6" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y6" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z6" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z6" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB6" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC6" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="33.0" customHeight="true">
       <c r="A7" t="s" s="6">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s" s="6">
         <v>59</v>
       </c>
-      <c r="B7" t="s" s="6">
+      <c r="C7" t="s" s="6">
+        <v>142</v>
+      </c>
+      <c r="D7" t="s" s="6">
         <v>60</v>
       </c>
-      <c r="C7" t="s" s="6">
-        <v>143</v>
-      </c>
-      <c r="D7" t="s" s="6">
+      <c r="E7" t="s" s="6">
         <v>61</v>
       </c>
-      <c r="E7" t="s" s="6">
+      <c r="F7" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I7" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K7" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q7" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R7" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T7" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="U7" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="F7" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G7" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="H7" t="s" s="7">
-        <v>53</v>
-      </c>
-      <c r="I7" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="J7" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="U7" t="s" s="10">
-        <v>30</v>
       </c>
       <c r="V7" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="W7" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="X7" s="11" t="s">
-        <v>55</v>
+      <c r="W7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="X7" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y7" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z7" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z7" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AA7" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB7" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC7" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="33.0" customHeight="true">
       <c r="A8" t="s" s="6">
+        <v>64</v>
+      </c>
+      <c r="B8" t="s" s="6">
         <v>65</v>
       </c>
-      <c r="B8" t="s" s="6">
+      <c r="C8" t="s" s="6">
+        <v>142</v>
+      </c>
+      <c r="D8" t="s" s="6">
         <v>66</v>
       </c>
-      <c r="C8" t="s" s="6">
-        <v>143</v>
-      </c>
-      <c r="D8" t="s" s="6">
-        <v>67</v>
-      </c>
       <c r="E8" t="s" s="6">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F8" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G8" t="s" s="7">
-        <v>45</v>
-      </c>
       <c r="H8" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="I8" t="s" s="7">
+        <v>44</v>
+      </c>
+      <c r="J8" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="K8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="L8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="O8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="P8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="Q8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="R8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="S8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="T8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="U8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="V8" t="s" s="10">
+        <v>29</v>
+      </c>
+      <c r="W8" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I8" t="s" s="7">
-        <v>45</v>
-      </c>
-      <c r="J8" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="K8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="M8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="N8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="O8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="P8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="R8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="T8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="U8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="V8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="W8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X8" s="10" t="s">
+      <c r="X8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="Y8" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="Z8" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="Y8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z8" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="AA8" s="11" t="s">
-        <v>55</v>
+      <c r="AA8" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="AB8" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="AC8" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="33.0" customHeight="true">
       <c r="A9" t="s" s="6">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s" s="6">
         <v>68</v>
       </c>
-      <c r="B9" t="s" s="6">
+      <c r="C9" t="s" s="6">
+        <v>142</v>
+      </c>
+      <c r="D9" t="s" s="6">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s" s="6">
         <v>69</v>
       </c>
-      <c r="C9" t="s" s="6">
-        <v>143</v>
-      </c>
-      <c r="D9" t="s" s="6">
-        <v>67</v>
-      </c>
-      <c r="E9" t="s" s="6">
-        <v>70</v>
-      </c>
       <c r="F9" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="G9" t="s" s="7">
-        <v>45</v>
-      </c>
       <c r="H9" t="s" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s" s="7">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J9" t="s" s="8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L9" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="L9" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="M9" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N9" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O9" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q9" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Q9" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="R9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S9" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="S9" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="T9" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U9" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="W9" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="W9" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="X9" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="Y9" t="s" s="12">
+        <v>29</v>
+      </c>
+      <c r="Z9" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="Y9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z9" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="AA9" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB9" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC9" t="s" s="10">
-        <v>30</v>
+      <c r="AA9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB9" t="s" s="10">
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="33.0" customHeight="true">
       <c r="A10" t="s" s="6">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s" s="6">
         <v>71</v>
       </c>
-      <c r="B10" t="s" s="6">
+      <c r="C10" t="s" s="6">
+        <v>142</v>
+      </c>
+      <c r="D10" t="s" s="6">
         <v>72</v>
       </c>
-      <c r="C10" t="s" s="6">
-        <v>143</v>
-      </c>
-      <c r="D10" t="s" s="6">
+      <c r="E10" t="s" s="6">
         <v>73</v>
       </c>
-      <c r="E10" t="s" s="6">
+      <c r="F10" t="s" s="8">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s" s="7">
         <v>74</v>
       </c>
-      <c r="F10" t="s" s="8">
-        <v>44</v>
-      </c>
-      <c r="G10" t="s" s="7">
-        <v>75</v>
-      </c>
       <c r="H10" t="s" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I10" t="s" s="7">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J10" t="s" s="8">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="L10" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="L10" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="M10" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N10" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O10" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P10" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="Q10" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Q10" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="R10" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="S10" t="s" s="10">
+        <v>29</v>
       </c>
       <c r="T10" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U10" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V10" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W10" t="s" s="10">
-        <v>30</v>
-      </c>
-      <c r="X10" t="s" s="10">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="X10" t="s" s="12">
+        <v>29</v>
       </c>
       <c r="Y10" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="Z10" t="s" s="12">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="Z10" s="10" t="s">
+        <v>148</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="AB10" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC10" s="11" t="s">
-        <v>77</v>
+        <v>63</v>
+      </c>
+      <c r="AB10" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC1"/>
+  <autoFilter ref="A1:AB1"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.25" right="0.25" top="0.75"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="2" fitToHeight="0"/>
 </worksheet>
